--- a/backtests/runs/20260505_170936/backtest_review.xlsx
+++ b/backtests/runs/20260505_170936/backtest_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://onedrive-global.kpmg.com/personal/weiliu3_kpmg_com_sg/Documents/Documents/Projects/Project X/CoCo AI Agent/CoCo_AI/backtests/runs/20260505_170936/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="11_7EF98A34D561A60E62355476585DCE3A8746A13C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD33FE6E-3002-422C-90B4-B7CA7F81F72E}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="11_7EF98A34D561A60E62355476585DCE3A8746A13C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33C11AC9-E17C-4538-892F-E9675905417A}"/>
   <bookViews>
     <workbookView xWindow="-30" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1279,7 +1279,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="300" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="300" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="300" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="300" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>15</v>
       </c>
@@ -1724,6 +1724,7 @@
     <filterColumn colId="13">
       <filters>
         <filter val="Strong"/>
+        <filter val="Weak"/>
       </filters>
     </filterColumn>
   </autoFilter>
